--- a/docs/纽北圈速榜.xlsx
+++ b/docs/纽北圈速榜.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fa87f9cddfddf65e/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="313" documentId="13_ncr:1_{4B0FD308-F9C8-4074-B815-1AEE4DD0BB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{170E6ACB-9F7C-4DD6-9011-849CDDD79C93}"/>
+  <xr:revisionPtr revIDLastSave="314" documentId="13_ncr:1_{4B0FD308-F9C8-4074-B815-1AEE4DD0BB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27C4766C-187B-4ED4-B52C-573C51C00070}"/>
   <bookViews>
-    <workbookView xWindow="1910" yWindow="2360" windowWidth="21950" windowHeight="13810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1910" yWindow="2190" windowWidth="21950" windowHeight="13810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8201,10 +8201,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>VEXARE</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>1002/798</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -8594,6 +8590,10 @@
   </si>
   <si>
     <t>F.S.R Break</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>VEXARE-X</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -10981,7 +10981,7 @@
         <v>2391</v>
       </c>
       <c r="E33" s="57" t="s">
-        <v>2392</v>
+        <v>2490</v>
       </c>
       <c r="F33" s="15">
         <v>4.6238425925925926E-3</v>
@@ -10993,7 +10993,7 @@
         <v>1.39</v>
       </c>
       <c r="I33" s="57" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="J33" s="57" t="s">
         <v>2388</v>
@@ -11528,7 +11528,7 @@
         <v>1833</v>
       </c>
       <c r="E46" s="57" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="F46" s="15">
         <v>4.7280092592592591E-3</v>
@@ -11540,10 +11540,10 @@
         <v>1.57</v>
       </c>
       <c r="I46" s="57" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="J46" s="57" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="K46" s="8">
         <v>2011</v>
@@ -11972,7 +11972,7 @@
         <v>2384</v>
       </c>
       <c r="E56" s="57" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="F56" s="15">
         <v>4.7928240740740743E-3</v>
@@ -11984,7 +11984,7 @@
         <v>2.1800000000000002</v>
       </c>
       <c r="I56" s="57" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="J56" s="57" t="s">
         <v>1474</v>
@@ -12215,7 +12215,7 @@
         <v>188</v>
       </c>
       <c r="D62" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>190</v>
@@ -12255,13 +12255,13 @@
         <v>14</v>
       </c>
       <c r="C63" s="57" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="D63" s="57" t="s">
         <v>1833</v>
       </c>
       <c r="E63" s="57" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="F63" s="15">
         <v>4.8124999999999999E-3</v>
@@ -12273,10 +12273,10 @@
         <v>2.34</v>
       </c>
       <c r="I63" s="64" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="J63" s="57" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="K63" s="8">
         <v>2016</v>
@@ -13488,13 +13488,13 @@
         <v>14</v>
       </c>
       <c r="C92" s="57" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="D92" s="57" t="s">
         <v>1833</v>
       </c>
       <c r="E92" s="57" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="F92" s="15">
         <v>4.9803240740740745E-3</v>
@@ -13506,10 +13506,10 @@
         <v>2.71</v>
       </c>
       <c r="I92" s="57" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="J92" s="57" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="K92" s="8">
         <v>2010</v>
@@ -14728,10 +14728,10 @@
         <v>15</v>
       </c>
       <c r="D121" s="57" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="E121" s="57" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="F121" s="15">
         <v>5.1122685185185186E-3</v>
@@ -14743,10 +14743,10 @@
         <v>2.76</v>
       </c>
       <c r="I121" s="57" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="J121" s="57" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="K121" s="8">
         <v>2019</v>
@@ -16284,10 +16284,10 @@
         <v>15</v>
       </c>
       <c r="D157" s="57" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="E157" s="57" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="F157" s="15">
         <v>5.2673611111111115E-3</v>
@@ -16299,10 +16299,10 @@
         <v>4.04</v>
       </c>
       <c r="I157" s="57" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="J157" s="57" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="K157" s="8">
         <v>2019</v>
@@ -16413,10 +16413,10 @@
         <v>15</v>
       </c>
       <c r="D160" s="57" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="E160" s="57" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="F160" s="15">
         <v>5.2824074074074075E-3</v>
@@ -16428,10 +16428,10 @@
         <v>4.22</v>
       </c>
       <c r="I160" s="57" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="J160" s="57" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="K160" s="8">
         <v>2019</v>
@@ -16581,7 +16581,7 @@
         <v>188</v>
       </c>
       <c r="D164" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E164" s="17" t="s">
         <v>391</v>
@@ -17256,10 +17256,10 @@
         <v>2071</v>
       </c>
       <c r="D180" s="57" t="s">
+        <v>2488</v>
+      </c>
+      <c r="E180" s="57" t="s">
         <v>2489</v>
-      </c>
-      <c r="E180" s="57" t="s">
-        <v>2490</v>
       </c>
       <c r="F180" s="15">
         <v>5.3333333333333332E-3</v>
@@ -17271,7 +17271,7 @@
         <v>3.9</v>
       </c>
       <c r="I180" s="57" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="J180" s="57" t="s">
         <v>1474</v>
@@ -17382,7 +17382,7 @@
         <v>2071</v>
       </c>
       <c r="D183" s="57" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="E183" s="57" t="s">
         <v>2073</v>
@@ -17397,7 +17397,7 @@
         <v>3.72</v>
       </c>
       <c r="I183" s="57" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="J183" s="57" t="s">
         <v>1474</v>
@@ -18636,7 +18636,7 @@
         <v>1945</v>
       </c>
       <c r="E212" s="57" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="F212" s="15">
         <v>5.3923611111111108E-3</v>
@@ -18648,10 +18648,10 @@
         <v>3.45</v>
       </c>
       <c r="I212" s="57" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="J212" s="57" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="K212" s="8">
         <v>2009</v>
@@ -19162,13 +19162,13 @@
         <v>14</v>
       </c>
       <c r="C224" s="57" t="s">
+        <v>2474</v>
+      </c>
+      <c r="D224" s="57" t="s">
+        <v>2437</v>
+      </c>
+      <c r="E224" s="57" t="s">
         <v>2475</v>
-      </c>
-      <c r="D224" s="57" t="s">
-        <v>2438</v>
-      </c>
-      <c r="E224" s="57" t="s">
-        <v>2476</v>
       </c>
       <c r="F224" s="15">
         <v>5.4074074074074076E-3</v>
@@ -19180,10 +19180,10 @@
         <v>4.29</v>
       </c>
       <c r="I224" s="57" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="J224" s="57" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="K224" s="8">
         <v>2019</v>
@@ -20071,10 +20071,10 @@
         <v>188</v>
       </c>
       <c r="D245" s="57" t="s">
+        <v>2395</v>
+      </c>
+      <c r="E245" s="57" t="s">
         <v>2396</v>
-      </c>
-      <c r="E245" s="57" t="s">
-        <v>2397</v>
       </c>
       <c r="F245" s="15">
         <v>5.4768518518518517E-3</v>
@@ -20086,10 +20086,10 @@
         <v>4.1399999999999997</v>
       </c>
       <c r="I245" s="57" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="J245" s="57" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="K245" s="8">
         <v>2020</v>
@@ -20101,7 +20101,7 @@
         <v>10.93</v>
       </c>
       <c r="O245" s="58" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.25">
@@ -20242,16 +20242,16 @@
         <v>247</v>
       </c>
       <c r="B249" s="61" t="s">
+        <v>2444</v>
+      </c>
+      <c r="C249" s="57" t="s">
         <v>2445</v>
-      </c>
-      <c r="C249" s="57" t="s">
-        <v>2446</v>
       </c>
       <c r="D249" s="17" t="s">
         <v>1945</v>
       </c>
       <c r="E249" s="57" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="F249" s="15">
         <v>5.4826388888888885E-3</v>
@@ -20263,10 +20263,10 @@
         <v>4.59</v>
       </c>
       <c r="I249" s="57" t="s">
+        <v>2446</v>
+      </c>
+      <c r="J249" s="57" t="s">
         <v>2447</v>
-      </c>
-      <c r="J249" s="57" t="s">
-        <v>2448</v>
       </c>
       <c r="K249" s="8">
         <v>2009</v>
@@ -20893,7 +20893,7 @@
         <v>188</v>
       </c>
       <c r="D264" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E264" s="8" t="s">
         <v>556</v>
@@ -22819,10 +22819,10 @@
         <v>15</v>
       </c>
       <c r="D309" s="57" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="E309" s="57" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="F309" s="15">
         <v>5.6365740740740742E-3</v>
@@ -22834,10 +22834,10 @@
         <v>6.2</v>
       </c>
       <c r="I309" s="57" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="J309" s="57" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="K309" s="8">
         <v>2019</v>
@@ -23374,10 +23374,10 @@
         <v>15</v>
       </c>
       <c r="D322" s="57" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="E322" s="57" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="F322" s="15">
         <v>5.6689814814814814E-3</v>
@@ -23389,10 +23389,10 @@
         <v>5.95</v>
       </c>
       <c r="I322" s="57" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="J322" s="57" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="K322" s="8">
         <v>2019</v>
@@ -23921,7 +23921,7 @@
         <v>188</v>
       </c>
       <c r="D335" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E335" s="8" t="s">
         <v>688</v>
@@ -24038,13 +24038,13 @@
         <v>74</v>
       </c>
       <c r="C338" s="57" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="D338" s="57" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="E338" s="57" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="F338" s="15">
         <v>5.7002314814814815E-3</v>
@@ -24056,7 +24056,7 @@
         <v>3.86</v>
       </c>
       <c r="I338" s="60" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="J338" s="8" t="s">
         <v>106</v>
@@ -24598,10 +24598,10 @@
         <v>15</v>
       </c>
       <c r="D351" s="57" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="E351" s="57" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="F351" s="15">
         <v>5.7395833333333326E-3</v>
@@ -24613,10 +24613,10 @@
         <v>6.14</v>
       </c>
       <c r="I351" s="64" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="J351" s="57" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="K351" s="8">
         <v>2019</v>
@@ -24730,7 +24730,7 @@
         <v>155</v>
       </c>
       <c r="E354" s="57" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="F354" s="15">
         <v>5.7442129629629596E-3</v>
@@ -24901,7 +24901,7 @@
         <v>188</v>
       </c>
       <c r="D358" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E358" s="8" t="s">
         <v>728</v>
@@ -24984,7 +24984,7 @@
         <v>2317</v>
       </c>
       <c r="E360" s="57" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="F360" s="15">
         <v>5.7557870370370376E-3</v>
@@ -24996,10 +24996,10 @@
         <v>6.06</v>
       </c>
       <c r="I360" s="57" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="J360" s="57" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="K360" s="8">
         <v>1998</v>
@@ -25018,16 +25018,16 @@
         <v>359</v>
       </c>
       <c r="B361" s="59" t="s">
+        <v>2458</v>
+      </c>
+      <c r="C361" s="57" t="s">
         <v>2459</v>
       </c>
-      <c r="C361" s="57" t="s">
-        <v>2460</v>
-      </c>
       <c r="D361" s="57" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="E361" s="57" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="F361" s="15">
         <v>5.7557870370370376E-3</v>
@@ -25039,10 +25039,10 @@
         <v>6.21</v>
       </c>
       <c r="I361" s="57" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="J361" s="57" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="K361" s="8">
         <v>2019</v>
@@ -25323,7 +25323,7 @@
         <v>2317</v>
       </c>
       <c r="E368" s="57" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="F368" s="15">
         <v>5.7685185185185183E-3</v>
@@ -25335,10 +25335,10 @@
         <v>6.29</v>
       </c>
       <c r="I368" s="57" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="J368" s="57" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="K368" s="8">
         <v>1998</v>
@@ -25714,7 +25714,7 @@
         <v>188</v>
       </c>
       <c r="D377" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E377" s="8" t="s">
         <v>751</v>
@@ -25896,7 +25896,7 @@
         <v>2317</v>
       </c>
       <c r="E381" s="57" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="F381" s="15">
         <v>5.8136574074074071E-3</v>
@@ -25908,10 +25908,10 @@
         <v>4.7</v>
       </c>
       <c r="I381" s="57" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="J381" s="57" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="K381" s="8">
         <v>2000</v>
@@ -25923,7 +25923,7 @@
         <v>11.84</v>
       </c>
       <c r="N381" s="62" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="O381" s="7"/>
     </row>
@@ -27079,7 +27079,7 @@
         <v>188</v>
       </c>
       <c r="D408" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E408" s="8" t="s">
         <v>801</v>
@@ -28497,7 +28497,7 @@
         <v>188</v>
       </c>
       <c r="D441" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E441" s="8" t="s">
         <v>840</v>
@@ -31902,7 +31902,7 @@
         <v>188</v>
       </c>
       <c r="D519" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E519" s="8" t="s">
         <v>955</v>
@@ -32250,10 +32250,10 @@
         <v>188</v>
       </c>
       <c r="D527" s="57" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="E527" s="57" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="F527" s="15">
         <v>6.1875000000000003E-3</v>
@@ -32265,10 +32265,10 @@
         <v>9.6300000000000008</v>
       </c>
       <c r="I527" s="64" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="J527" s="57" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="K527" s="8">
         <v>2020</v>
@@ -34155,7 +34155,7 @@
         <v>188</v>
       </c>
       <c r="D571" s="57" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="E571" s="8" t="s">
         <v>1026</v>
@@ -34243,7 +34243,7 @@
         <v>188</v>
       </c>
       <c r="D573" s="57" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="E573" s="8" t="s">
         <v>1028</v>
@@ -34602,7 +34602,7 @@
         <v>2317</v>
       </c>
       <c r="E581" s="57" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="F581" s="15">
         <v>6.2986111111111116E-3</v>
@@ -34614,10 +34614,10 @@
         <v>11.73</v>
       </c>
       <c r="I581" s="64" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="J581" s="57" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="K581" s="8">
         <v>1998</v>
@@ -35488,7 +35488,7 @@
         <v>188</v>
       </c>
       <c r="D602" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E602" s="8" t="s">
         <v>1079</v>
@@ -35875,10 +35875,10 @@
         <v>15</v>
       </c>
       <c r="D611" s="57" t="s">
+        <v>2437</v>
+      </c>
+      <c r="E611" s="57" t="s">
         <v>2438</v>
-      </c>
-      <c r="E611" s="57" t="s">
-        <v>2439</v>
       </c>
       <c r="F611" s="15">
         <v>6.4155092592592588E-3</v>
@@ -35890,10 +35890,10 @@
         <v>10.86</v>
       </c>
       <c r="I611" s="57" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="J611" s="57" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="K611" s="8">
         <v>2018</v>
@@ -36258,7 +36258,7 @@
         <v>188</v>
       </c>
       <c r="D620" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E620" s="8" t="s">
         <v>1103</v>
@@ -37216,7 +37216,7 @@
         <v>188</v>
       </c>
       <c r="D643" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E643" s="8" t="s">
         <v>1133</v>
@@ -37980,7 +37980,7 @@
         <v>188</v>
       </c>
       <c r="D661" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E661" s="8" t="s">
         <v>1160</v>
@@ -39311,10 +39311,10 @@
         <v>547</v>
       </c>
       <c r="D692" s="57" t="s">
+        <v>2480</v>
+      </c>
+      <c r="E692" s="57" t="s">
         <v>2481</v>
-      </c>
-      <c r="E692" s="57" t="s">
-        <v>2482</v>
       </c>
       <c r="F692" s="15">
         <v>6.7291666666666663E-3</v>
@@ -39326,10 +39326,10 @@
         <v>10.51</v>
       </c>
       <c r="I692" s="57" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="J692" s="57" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="K692" s="8">
         <v>2003</v>
@@ -40819,7 +40819,7 @@
         <v>188</v>
       </c>
       <c r="D727" s="57" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="E727" s="8" t="s">
         <v>1256</v>
@@ -41597,7 +41597,7 @@
         <v>188</v>
       </c>
       <c r="D746" s="57" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E746" s="8" t="s">
         <v>1293</v>
@@ -43155,10 +43155,10 @@
         <v>331</v>
       </c>
       <c r="D783" s="57" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="E783" s="57" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="F783" s="15">
         <v>7.5370370370370374E-3</v>
@@ -43167,10 +43167,10 @@
         <v>11.08</v>
       </c>
       <c r="H783" s="66" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="I783" s="60" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="J783" s="8" t="s">
         <v>106</v>
@@ -43185,7 +43185,7 @@
         <v>18.28</v>
       </c>
       <c r="N783" s="62" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="O783" s="7"/>
     </row>
@@ -43451,13 +43451,13 @@
         <v>74</v>
       </c>
       <c r="C790" s="57" t="s">
+        <v>2427</v>
+      </c>
+      <c r="D790" s="57" t="s">
         <v>2428</v>
       </c>
-      <c r="D790" s="57" t="s">
+      <c r="E790" s="57" t="s">
         <v>2429</v>
-      </c>
-      <c r="E790" s="57" t="s">
-        <v>2430</v>
       </c>
       <c r="F790" s="15">
         <v>7.7025462962962959E-3</v>
@@ -43466,13 +43466,13 @@
         <v>9.16</v>
       </c>
       <c r="H790" s="66" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="I790" s="57" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="J790" s="57" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="K790" s="8">
         <v>1995</v>
